--- a/output/topology_excel/1852.xlsx
+++ b/output/topology_excel/1852.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B21" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B23" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B24" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B27" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B28" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B29" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B30" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B31" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B32" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B33" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B34" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B35" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B36" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B37" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="B38" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="B39" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B40" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B41" t="n">
         <v>46</v>
@@ -1334,10 +1334,76 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
+        <v>134</v>
+      </c>
+      <c r="F41" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>10</v>
+      </c>
+      <c r="B42" t="n">
+        <v>45</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
         <v>90</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F42" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>21</v>
+      </c>
+      <c r="B43" t="n">
+        <v>45</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>97</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>21</v>
+      </c>
+      <c r="B44" t="n">
+        <v>46</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>214</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/1852.xlsx
+++ b/output/topology_excel/1852.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
